--- a/Convert_from_xlsx_to_Json/table_normalization/education-table34.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table34.xlsx
@@ -590,37 +590,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1106,21 +1106,21 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25">
       <c r="A1" s="1"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="45" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1178,28 +1178,28 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="23" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I4" s="14" t="s">
@@ -1207,39 +1207,39 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" customHeight="1">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="17"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" ht="45" customHeight="1">
-      <c r="A6" s="15"/>
+      <c r="A6" s="21"/>
       <c r="B6" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
       <c r="G6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="18"/>
       <c r="I6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="45" customHeight="1">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -1268,19 +1268,19 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="45" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="24" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -1289,55 +1289,55 @@
       <c r="G8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45" customHeight="1">
-      <c r="A9" s="23"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="7" t="s">
         <v>51</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" ht="45" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="18"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="7" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="I8:I10"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="E8:E10"/>
